--- a/offers/عروض الحليب والحفايض.xlsx
+++ b/offers/عروض الحليب والحفايض.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YAHAY ZAQZOUQ\IMPORTANT\ملفات العروض\8\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YAHAY ZAQZOUQ\IMPORTANT\ملفات العروض\8\New folder\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00FDFFDE-D71C-4917-9B3F-BBA0C0D1031B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A135D14D-EEC1-47F7-B977-42F1269DED51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="107">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -332,6 +332,15 @@
   </si>
   <si>
     <t>خصم</t>
+  </si>
+  <si>
+    <t>[] نيدو احمر بالعسل (3) 900 جرام</t>
+  </si>
+  <si>
+    <t>حبتين</t>
+  </si>
+  <si>
+    <t>0003070</t>
   </si>
 </sst>
 </file>
@@ -1894,8 +1903,27 @@
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="C50" s="3"/>
-      <c r="D50" s="3"/>
+      <c r="A50" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="B50" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C50" s="3">
+        <v>67.8</v>
+      </c>
+      <c r="D50" s="3">
+        <v>109.8</v>
+      </c>
+      <c r="E50" s="4">
+        <v>46267</v>
+      </c>
+      <c r="F50" s="5">
+        <v>46260</v>
+      </c>
+      <c r="G50" s="1" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="C51" s="3"/>

--- a/offers/عروض الحليب والحفايض.xlsx
+++ b/offers/عروض الحليب والحفايض.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YAHAY ZAQZOUQ\IMPORTANT\ملفات العروض\8\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YAHAY ZAQZOUQ\IMPORTANT\ملفات العروض\8\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A135D14D-EEC1-47F7-B977-42F1269DED51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5FDAFA-43DE-4CE5-8E94-2A9BF90A40BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -334,13 +334,13 @@
     <t>خصم</t>
   </si>
   <si>
-    <t>[] نيدو احمر بالعسل (3) 900 جرام</t>
-  </si>
-  <si>
     <t>حبتين</t>
   </si>
   <si>
     <t>0003070</t>
+  </si>
+  <si>
+    <t>نيدو احمر بالعسل (3) 900 جرام</t>
   </si>
 </sst>
 </file>
@@ -1904,10 +1904,10 @@
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="C50" s="3">
         <v>67.8</v>
@@ -1922,7 +1922,7 @@
         <v>46260</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">

--- a/offers/عروض الحليب والحفايض.xlsx
+++ b/offers/عروض الحليب والحفايض.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YAHAY ZAQZOUQ\IMPORTANT\ملفات العروض\8\GitHub\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBD7BC18-FE1D-4F40-8355-82CD4B62F9E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C43B01D2-8F55-4085-8602-97AC2093EDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="106">
   <si>
     <t>كود الصنف</t>
   </si>
@@ -332,9 +332,6 @@
   </si>
   <si>
     <t>خصم</t>
-  </si>
-  <si>
-    <t>حبتين</t>
   </si>
   <si>
     <t>0003070</t>
@@ -800,10 +797,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="C2" s="3">
         <v>67.8</v>
@@ -818,7 +815,7 @@
         <v>46260</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
